--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Mistral-7B-Instruct-v0.3/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Mistral-7B-Instruct-v0.3/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8225806451612904</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.8309859154929577</v>
+        <v>0.823943661971831</v>
       </c>
       <c r="D2">
-        <v>0.32</v>
+        <v>0.3623188405797101</v>
       </c>
       <c r="E2">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
